--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486314_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486314_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2496</v>
+        <v>3.826</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7382</v>
+        <v>2.8694</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5114</v>
+        <v>0.9566</v>
       </c>
       <c r="G2" t="n">
         <v>-0.7013</v>
@@ -610,13 +610,13 @@
         <v>3.0451</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1032</v>
+        <v>0.6796</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5418</v>
+        <v>0.673</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5614</v>
+        <v>0.0066</v>
       </c>
       <c r="V2" t="n">
         <v>1.8902</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.868</v>
+        <v>2.6425</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4393</v>
+        <v>1.9981</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4287</v>
+        <v>0.6444</v>
       </c>
       <c r="G3" t="n">
         <v>0.83</v>
@@ -688,13 +688,13 @@
         <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9641</v>
+        <v>-0.1896</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2139</v>
+        <v>0.3449</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7502</v>
+        <v>-0.5345</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3904</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. NICOLAU ALEDON</t>
+          <t>L. TERRY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4311</v>
+        <v>0.1968</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6263</v>
+        <v>-1.0716</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1952</v>
+        <v>1.2684</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0182</v>
+        <v>0.1803</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0182</v>
+        <v>1.3963</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-1.216</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0182</v>
+        <v>0.9016</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0182</v>
+        <v>1.7797</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.8781</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.3834</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.3379</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6081</v>
+        <v>0.1247</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6081</v>
+        <v>0.2019</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.0772</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1952</v>
+        <v>0.5443</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1952</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>J. NICOLAU ALEDON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0699</v>
+        <v>0.1643</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.719</v>
+        <v>0.3595</v>
       </c>
       <c r="F5" t="n">
-        <v>2.649</v>
+        <v>-0.1952</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.4385</v>
+        <v>0.0182</v>
       </c>
       <c r="H5" t="n">
-        <v>0.301</v>
+        <v>0.0182</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.7395</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.6233</v>
+        <v>0.0182</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5411</v>
+        <v>0.0182</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.0822</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1848</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8421999999999999</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3426</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.435</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9781</v>
+        <v>0.3413</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4937</v>
+        <v>0.3413</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4844</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1745</v>
+        <v>-0.1952</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5857</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7602</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. TERRY</t>
+          <t>G. MAIZA APECECHEA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4296</v>
+        <v>-0.7834</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5439</v>
+        <v>-1.0837</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1142</v>
+        <v>0.3003</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1803</v>
+        <v>-0.2345</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3963</v>
+        <v>0.2006</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.216</v>
+        <v>-0.4351</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9016</v>
+        <v>-0.2296</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7797</v>
+        <v>0.0365</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8781</v>
+        <v>-0.2661</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.0049</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3834</v>
+        <v>0.1641</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3379</v>
+        <v>-0.1689</v>
       </c>
       <c r="P6" t="n">
         <v>-0.6525</v>
@@ -922,28 +922,28 @@
         <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5017</v>
+        <v>0.1036</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2704</v>
+        <v>0.1911</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2313</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5443</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5443</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. ROSA POMPIDO</t>
+          <t>M. MOTOS CABODEVILLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.162</v>
+        <v>-0.9072</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5155</v>
+        <v>-0.6473</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6775</v>
+        <v>-0.2599</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3345</v>
+        <v>-1.6895</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3345</v>
+        <v>-1.0735</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0.616</v>
       </c>
       <c r="J7" t="n">
-        <v>0.584</v>
+        <v>-0.7086</v>
       </c>
       <c r="K7" t="n">
-        <v>0.584</v>
+        <v>-0.7086</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2495</v>
+        <v>-0.981</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2495</v>
+        <v>-0.365</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.616</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3665</v>
+        <v>-0.0877</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.298</v>
+        <v>-0.149</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MOTOS CABODEVILLA</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2425</v>
+        <v>-1.0612</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9825</v>
+        <v>-3.4328</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2599</v>
+        <v>2.3716</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6895</v>
+        <v>-1.4385</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0735</v>
+        <v>0.301</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.616</v>
+        <v>-1.7395</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7086</v>
+        <v>-2.6233</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7086</v>
+        <v>-0.5411</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-2.0822</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.981</v>
+        <v>1.1848</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.365</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.616</v>
+        <v>0.3426</v>
       </c>
       <c r="P8" t="n">
-        <v>0.87</v>
+        <v>-0.435</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.423</v>
+        <v>0.9869</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.274</v>
+        <v>0.7799</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.149</v>
+        <v>0.207</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.1745</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5857</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. MAIZA APECECHEA</t>
+          <t>I. ROSA POMPIDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7382</v>
+        <v>-1.162</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8227</v>
+        <v>0.5155</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08450000000000001</v>
+        <v>-1.6775</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2345</v>
+        <v>0.3345</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2006</v>
+        <v>0.3345</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4351</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2296</v>
+        <v>0.584</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0365</v>
+        <v>0.584</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2661</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0049</v>
+        <v>-0.2495</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1641</v>
+        <v>-0.2495</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1689</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8512</v>
+        <v>-0.3665</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.548</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3032</v>
+        <v>-0.298</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-1.13</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5794</v>
+        <v>-1.449</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.654</v>
+        <v>-3.5544</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0746</v>
+        <v>2.1054</v>
       </c>
       <c r="G10" t="n">
         <v>-4.3754</v>
@@ -1234,13 +1234,13 @@
         <v>1.9576</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.769</v>
+        <v>0.3614</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5444</v>
+        <v>0.5552</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2246</v>
+        <v>-0.1938</v>
       </c>
       <c r="V10" t="n">
         <v>1.695</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. ANSORREGUI DEBA</t>
+          <t>I. ARROYO VARELA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.273</v>
+        <v>-1.8074</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0372</v>
+        <v>-2.8041</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3102</v>
+        <v>0.9968</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1018</v>
+        <v>-2.7626</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1368</v>
+        <v>-1.7275</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.965</v>
+        <v>-1.0351</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3661</v>
+        <v>-2.321</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6451</v>
+        <v>-1.1767</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.0112</v>
+        <v>-1.1442</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7357</v>
+        <v>-0.4417</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7819</v>
+        <v>-0.5508</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9539</v>
+        <v>0.1091</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3926</v>
+        <v>1.9576</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3058</v>
+        <v>-0.3052</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3179</v>
+        <v>0.2139</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0121</v>
+        <v>-0.5191</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.6944</v>
+        <v>0.3904</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.7395</v>
+        <v>0.3904</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.9549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. ARROYO VARELA</t>
+          <t>M. ANSORREGUI DEBA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4888</v>
+        <v>-5.0667</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2389</v>
+        <v>-1.7257</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7502</v>
+        <v>-3.341</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7626</v>
+        <v>-2.1018</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.7275</v>
+        <v>-0.1368</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0351</v>
+        <v>-1.965</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.321</v>
+        <v>-0.3661</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1767</v>
+        <v>0.6451</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1442</v>
+        <v>-1.0112</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4417</v>
+        <v>-1.7357</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5508</v>
+        <v>-0.7819</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1091</v>
+        <v>-0.9539</v>
       </c>
       <c r="P12" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9576</v>
+        <v>2.3926</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9866</v>
+        <v>1.512</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2209</v>
+        <v>1.555</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7657</v>
+        <v>-0.043</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3904</v>
+        <v>-4.6944</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3904</v>
+        <v>-0.7395</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-3.9549</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.434699999999999</v>
+        <v>-5.407299999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.604499999999998</v>
+        <v>-8.5771</v>
       </c>
       <c r="F13" t="n">
-        <v>3.169800000000001</v>
+        <v>3.169899999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-11.9406</v>
@@ -1441,7 +1441,7 @@
         <v>-13.9329</v>
       </c>
       <c r="J13" t="n">
-        <v>-8.130600000000001</v>
+        <v>-8.130599999999999</v>
       </c>
       <c r="K13" t="n">
         <v>3.5911</v>
@@ -1468,13 +1468,13 @@
         <v>17.4006</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1331</v>
+        <v>3.1605</v>
       </c>
       <c r="T13" t="n">
-        <v>3.821399999999999</v>
+        <v>4.849</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.6883</v>
+        <v>-1.6884</v>
       </c>
       <c r="V13" t="n">
         <v>-2.0646</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.037100000000001</v>
+        <v>9.1745</v>
       </c>
       <c r="E14" t="n">
-        <v>7.765</v>
+        <v>7.8767</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2721</v>
+        <v>1.2978</v>
       </c>
       <c r="G14" t="n">
         <v>9.8743</v>
@@ -1546,13 +1546,13 @@
         <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1423</v>
+        <v>-0.0048</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0721</v>
+        <v>0.1839</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2144</v>
+        <v>-0.1887</v>
       </c>
       <c r="V14" t="n">
         <v>-1.13</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.4386</v>
+        <v>4.3789</v>
       </c>
       <c r="E15" t="n">
-        <v>2.591</v>
+        <v>1.8087</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8476</v>
+        <v>2.5702</v>
       </c>
       <c r="G15" t="n">
         <v>1.6513</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3326</v>
+        <v>1.2729</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9852</v>
+        <v>1.2029</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3474</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>3.1947</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1646</v>
+        <v>2.9083</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8325</v>
+        <v>3.3913</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6679</v>
+        <v>-0.483</v>
       </c>
       <c r="G16" t="n">
         <v>5.4939</v>
@@ -1702,13 +1702,13 @@
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2418</v>
+        <v>-0.4981</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3305</v>
+        <v>0.2283</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9114</v>
+        <v>-0.7264</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5649999999999999</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4348</v>
+        <v>1.0829</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1635</v>
+        <v>-0.387</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5984</v>
+        <v>1.47</v>
       </c>
       <c r="G17" t="n">
         <v>1.2651</v>
@@ -1780,13 +1780,13 @@
         <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6695</v>
+        <v>0.3175</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8292</v>
+        <v>0.6057</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1597</v>
+        <v>-0.2881</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9347</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8591</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2381</v>
+        <v>-0.1263</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0972</v>
+        <v>0.8506</v>
       </c>
       <c r="G18" t="n">
         <v>0.7856</v>
@@ -1858,13 +1858,13 @@
         <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3615</v>
+        <v>-0.4963</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4795</v>
+        <v>-0.3677</v>
       </c>
       <c r="U18" t="n">
-        <v>0.118</v>
+        <v>-0.1286</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5157</v>
+        <v>-0.1163</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5885</v>
+        <v>-2.9238</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0728</v>
+        <v>2.8075</v>
       </c>
       <c r="G19" t="n">
         <v>-2.7595</v>
@@ -1936,13 +1936,13 @@
         <v>2.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.798</v>
+        <v>-0.3987</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6117</v>
+        <v>0.2764</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.4097</v>
+        <v>-0.6751</v>
       </c>
       <c r="V19" t="n">
         <v>4.1294</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1272</v>
+        <v>-1.7124</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.512</v>
+        <v>-3.4003</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3848</v>
+        <v>1.6879</v>
       </c>
       <c r="G20" t="n">
         <v>-3.2827</v>
@@ -2014,13 +2014,13 @@
         <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7793</v>
+        <v>-0.3644</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0156</v>
+        <v>0.1274</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-0.4918</v>
       </c>
       <c r="V20" t="n">
         <v>1.4997</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6996</v>
+        <v>-3.3772</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7322</v>
+        <v>-3.6204</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0326</v>
+        <v>0.2432</v>
       </c>
       <c r="G21" t="n">
         <v>0.8174</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3</v>
+        <v>-0.9776</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.5732</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.615</v>
+        <v>-0.4044</v>
       </c>
       <c r="V21" t="n">
         <v>-2.9995</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.157</v>
+        <v>-5.8834</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.1241</v>
+        <v>-5.7888</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.033</v>
+        <v>-0.0946</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9048</v>
@@ -2170,13 +2170,13 @@
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5122</v>
+        <v>-0.2385</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3305</v>
+        <v>0.0048</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1817</v>
+        <v>-0.2434</v>
       </c>
       <c r="V22" t="n">
         <v>-1.13</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>6.434699999999999</v>
+        <v>7.179599999999999</v>
       </c>
       <c r="E23" t="n">
         <v>-3.1699</v>
       </c>
       <c r="F23" t="n">
-        <v>9.6046</v>
+        <v>10.3496</v>
       </c>
       <c r="G23" t="n">
         <v>11.9406</v>
@@ -2248,13 +2248,13 @@
         <v>11.9628</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.133</v>
+        <v>-1.388</v>
       </c>
       <c r="T23" t="n">
-        <v>1.6883</v>
+        <v>1.6885</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.8214</v>
+        <v>-3.0765</v>
       </c>
       <c r="V23" t="n">
         <v>2.064600000000001</v>
